--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I925"/>
+  <dimension ref="A1:I1167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36499,6 +36499,9444 @@
         </is>
       </c>
     </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B926" t="n">
+        <v>1</v>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D926" t="n">
+        <v>7</v>
+      </c>
+      <c r="E926" t="n">
+        <v>63</v>
+      </c>
+      <c r="F926" t="n">
+        <v>7</v>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B927" t="n">
+        <v>2</v>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D927" t="n">
+        <v>19</v>
+      </c>
+      <c r="E927" t="n">
+        <v>208</v>
+      </c>
+      <c r="F927" t="n">
+        <v>5</v>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B928" t="n">
+        <v>3</v>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D928" t="n">
+        <v>5</v>
+      </c>
+      <c r="E928" t="n">
+        <v>980</v>
+      </c>
+      <c r="F928" t="n">
+        <v>54</v>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B929" t="n">
+        <v>4</v>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D929" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E929" t="n">
+        <v>26</v>
+      </c>
+      <c r="F929" t="n">
+        <v>1</v>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>5</v>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D930" t="n">
+        <v>9</v>
+      </c>
+      <c r="E930" t="n">
+        <v>640</v>
+      </c>
+      <c r="F930" t="n">
+        <v>25</v>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>6</v>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D931" t="n">
+        <v>7</v>
+      </c>
+      <c r="E931" t="n">
+        <v>720</v>
+      </c>
+      <c r="F931" t="n">
+        <v>38</v>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>7</v>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D932" t="n">
+        <v>8</v>
+      </c>
+      <c r="E932" t="n">
+        <v>530</v>
+      </c>
+      <c r="F932" t="n">
+        <v>22</v>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B933" t="n">
+        <v>8</v>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D933" t="n">
+        <v>4</v>
+      </c>
+      <c r="E933" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F933" t="n">
+        <v>118</v>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B934" t="n">
+        <v>9</v>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D934" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E934" t="n">
+        <v>29</v>
+      </c>
+      <c r="F934" t="n">
+        <v>1</v>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B935" t="n">
+        <v>10</v>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D935" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E935" t="n">
+        <v>870</v>
+      </c>
+      <c r="F935" t="n">
+        <v>46</v>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B936" t="n">
+        <v>11</v>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D936" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E936" t="n">
+        <v>18</v>
+      </c>
+      <c r="F936" t="n">
+        <v>1</v>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>5.56%</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B937" t="n">
+        <v>12</v>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D937" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E937" t="n">
+        <v>480</v>
+      </c>
+      <c r="F937" t="n">
+        <v>18</v>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B938" t="n">
+        <v>13</v>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D938" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E938" t="n">
+        <v>6</v>
+      </c>
+      <c r="F938" t="n">
+        <v>1</v>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B939" t="n">
+        <v>14</v>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D939" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E939" t="n">
+        <v>590</v>
+      </c>
+      <c r="F939" t="n">
+        <v>26</v>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B940" t="n">
+        <v>15</v>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D940" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E940" t="n">
+        <v>820</v>
+      </c>
+      <c r="F940" t="n">
+        <v>45</v>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>16</v>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D941" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E941" t="n">
+        <v>760</v>
+      </c>
+      <c r="F941" t="n">
+        <v>38</v>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>17</v>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D942" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E942" t="n">
+        <v>930</v>
+      </c>
+      <c r="F942" t="n">
+        <v>58</v>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>18</v>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D943" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E943" t="n">
+        <v>880</v>
+      </c>
+      <c r="F943" t="n">
+        <v>52</v>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>19</v>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D944" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E944" t="n">
+        <v>44</v>
+      </c>
+      <c r="F944" t="n">
+        <v>1</v>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>20</v>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D945" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E945" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F945" t="n">
+        <v>168</v>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>21</v>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D946" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E946" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F946" t="n">
+        <v>121</v>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>22</v>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D947" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E947" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F947" t="n">
+        <v>104</v>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>1</v>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D948" t="n">
+        <v>7</v>
+      </c>
+      <c r="E948" t="n">
+        <v>63</v>
+      </c>
+      <c r="F948" t="n">
+        <v>7</v>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>2</v>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D949" t="n">
+        <v>19</v>
+      </c>
+      <c r="E949" t="n">
+        <v>208</v>
+      </c>
+      <c r="F949" t="n">
+        <v>5</v>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>3</v>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D950" t="n">
+        <v>5</v>
+      </c>
+      <c r="E950" t="n">
+        <v>980</v>
+      </c>
+      <c r="F950" t="n">
+        <v>54</v>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>4</v>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D951" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E951" t="n">
+        <v>26</v>
+      </c>
+      <c r="F951" t="n">
+        <v>1</v>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>5</v>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D952" t="n">
+        <v>9</v>
+      </c>
+      <c r="E952" t="n">
+        <v>640</v>
+      </c>
+      <c r="F952" t="n">
+        <v>25</v>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>6</v>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D953" t="n">
+        <v>7</v>
+      </c>
+      <c r="E953" t="n">
+        <v>720</v>
+      </c>
+      <c r="F953" t="n">
+        <v>38</v>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>7</v>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D954" t="n">
+        <v>8</v>
+      </c>
+      <c r="E954" t="n">
+        <v>530</v>
+      </c>
+      <c r="F954" t="n">
+        <v>22</v>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>8</v>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D955" t="n">
+        <v>4</v>
+      </c>
+      <c r="E955" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F955" t="n">
+        <v>118</v>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>9</v>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D956" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E956" t="n">
+        <v>29</v>
+      </c>
+      <c r="F956" t="n">
+        <v>1</v>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>10</v>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D957" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E957" t="n">
+        <v>870</v>
+      </c>
+      <c r="F957" t="n">
+        <v>46</v>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>11</v>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E958" t="n">
+        <v>18</v>
+      </c>
+      <c r="F958" t="n">
+        <v>1</v>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>5.56%</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>12</v>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E959" t="n">
+        <v>480</v>
+      </c>
+      <c r="F959" t="n">
+        <v>18</v>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>13</v>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E960" t="n">
+        <v>6</v>
+      </c>
+      <c r="F960" t="n">
+        <v>1</v>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>14</v>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E961" t="n">
+        <v>590</v>
+      </c>
+      <c r="F961" t="n">
+        <v>26</v>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>15</v>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E962" t="n">
+        <v>820</v>
+      </c>
+      <c r="F962" t="n">
+        <v>45</v>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>16</v>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E963" t="n">
+        <v>760</v>
+      </c>
+      <c r="F963" t="n">
+        <v>38</v>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>17</v>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E964" t="n">
+        <v>930</v>
+      </c>
+      <c r="F964" t="n">
+        <v>58</v>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>18</v>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E965" t="n">
+        <v>880</v>
+      </c>
+      <c r="F965" t="n">
+        <v>52</v>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>19</v>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E966" t="n">
+        <v>44</v>
+      </c>
+      <c r="F966" t="n">
+        <v>1</v>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>20</v>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E967" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F967" t="n">
+        <v>168</v>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>21</v>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E968" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F968" t="n">
+        <v>121</v>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>22</v>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E969" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F969" t="n">
+        <v>104</v>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>1</v>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E970" t="n">
+        <v>70</v>
+      </c>
+      <c r="F970" t="n">
+        <v>7</v>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>2</v>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E971" t="n">
+        <v>227</v>
+      </c>
+      <c r="F971" t="n">
+        <v>5</v>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>3</v>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>5</v>
+      </c>
+      <c r="E972" t="n">
+        <v>980</v>
+      </c>
+      <c r="F972" t="n">
+        <v>54</v>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>4</v>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E973" t="n">
+        <v>27</v>
+      </c>
+      <c r="F973" t="n">
+        <v>1</v>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>5</v>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>9</v>
+      </c>
+      <c r="E974" t="n">
+        <v>640</v>
+      </c>
+      <c r="F974" t="n">
+        <v>25</v>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>6</v>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>7</v>
+      </c>
+      <c r="E975" t="n">
+        <v>720</v>
+      </c>
+      <c r="F975" t="n">
+        <v>38</v>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>7</v>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>8</v>
+      </c>
+      <c r="E976" t="n">
+        <v>530</v>
+      </c>
+      <c r="F976" t="n">
+        <v>22</v>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>8</v>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>4</v>
+      </c>
+      <c r="E977" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F977" t="n">
+        <v>118</v>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>9</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E978" t="n">
+        <v>34</v>
+      </c>
+      <c r="F978" t="n">
+        <v>1</v>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>10</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E979" t="n">
+        <v>870</v>
+      </c>
+      <c r="F979" t="n">
+        <v>46</v>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>11</v>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E980" t="n">
+        <v>22</v>
+      </c>
+      <c r="F980" t="n">
+        <v>1</v>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>12</v>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E981" t="n">
+        <v>480</v>
+      </c>
+      <c r="F981" t="n">
+        <v>18</v>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>13</v>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E982" t="n">
+        <v>6</v>
+      </c>
+      <c r="F982" t="n">
+        <v>1</v>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>14</v>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E983" t="n">
+        <v>590</v>
+      </c>
+      <c r="F983" t="n">
+        <v>26</v>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>15</v>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E984" t="n">
+        <v>820</v>
+      </c>
+      <c r="F984" t="n">
+        <v>45</v>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>16</v>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E985" t="n">
+        <v>760</v>
+      </c>
+      <c r="F985" t="n">
+        <v>38</v>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>17</v>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E986" t="n">
+        <v>930</v>
+      </c>
+      <c r="F986" t="n">
+        <v>58</v>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>18</v>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E987" t="n">
+        <v>880</v>
+      </c>
+      <c r="F987" t="n">
+        <v>52</v>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>19</v>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>41</v>
+      </c>
+      <c r="E988" t="n">
+        <v>51</v>
+      </c>
+      <c r="F988" t="n">
+        <v>1</v>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>20</v>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E989" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F989" t="n">
+        <v>168</v>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>21</v>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E990" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F990" t="n">
+        <v>121</v>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>22</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E991" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F991" t="n">
+        <v>104</v>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>1</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E992" t="n">
+        <v>71</v>
+      </c>
+      <c r="F992" t="n">
+        <v>7</v>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>9.86%</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>2</v>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D993" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E993" t="n">
+        <v>244</v>
+      </c>
+      <c r="F993" t="n">
+        <v>5</v>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>3</v>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D994" t="n">
+        <v>5</v>
+      </c>
+      <c r="E994" t="n">
+        <v>980</v>
+      </c>
+      <c r="F994" t="n">
+        <v>54</v>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>4</v>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D995" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E995" t="n">
+        <v>27</v>
+      </c>
+      <c r="F995" t="n">
+        <v>1</v>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>5</v>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D996" t="n">
+        <v>9</v>
+      </c>
+      <c r="E996" t="n">
+        <v>640</v>
+      </c>
+      <c r="F996" t="n">
+        <v>25</v>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>6</v>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D997" t="n">
+        <v>7</v>
+      </c>
+      <c r="E997" t="n">
+        <v>720</v>
+      </c>
+      <c r="F997" t="n">
+        <v>38</v>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>7</v>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D998" t="n">
+        <v>8</v>
+      </c>
+      <c r="E998" t="n">
+        <v>530</v>
+      </c>
+      <c r="F998" t="n">
+        <v>22</v>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>8</v>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>4</v>
+      </c>
+      <c r="E999" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F999" t="n">
+        <v>118</v>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>4.35%</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>9.72%</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1015" t="n">
+        <v>19</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>246</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1016" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1017" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1017" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1018" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1019" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1019" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1020" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1021" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1021" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1022" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1022" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1023" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1023" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1024" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1024" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>4.35%</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1025" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1025" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1026" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1026" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1027" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1027" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1028" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1028" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1029" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1029" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1030" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1031" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1031" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1032" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1032" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1033" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1033" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1034" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1034" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1035" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1035" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1036" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1036" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>9.72%</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1037" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>252</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1038" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1039" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1040" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1041" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1042" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1042" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1043" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1043" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1044" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1044" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1045" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1045" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1046" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1046" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1047" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1047" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1048" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1048" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1049" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1049" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1050" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1050" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1051" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1051" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1052" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1052" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1053" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1053" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1054" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1054" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1055" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1055" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1056" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1056" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1057" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1058" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>9.21%</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1059" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>266</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1060" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1061" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1062" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1063" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1064" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1065" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1066" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>2.70%</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1067" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1068" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1069" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1070" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1071" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1072" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1073" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1074" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1075" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1076" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1077" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1078" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1079" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1080" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>9.21%</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1081" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>269</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1082" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1083" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1084" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1085" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1086" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1087" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1088" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>2.70%</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1089" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1090" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1091" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1092" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1093" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1094" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1095" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1096" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1097" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1098" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1099" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1099" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1100" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1100" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B1101" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1101" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1102" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>9.21%</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1103" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>275</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>2.18%</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1104" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1105" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1106" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1106" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1107" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1107" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1108" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1108" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1109" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1109" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1110" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1110" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1111" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1111" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1112" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>4.00%</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1113" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1113" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1114" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1114" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>14.29%</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1115" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1115" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1116" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1116" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1117" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1117" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1118" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1118" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1119" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1119" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1120" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1120" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>3.08%</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1121" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1121" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1122" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1122" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B1123" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1123" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1124" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>8.97%</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1125" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1125" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>2.33%</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1126" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1126" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1127" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1127" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1128" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1128" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1129" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1129" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1130" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1130" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1131" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1131" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1132" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1132" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>2.44%</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1133" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1133" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1134" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1134" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>4.00%</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1135" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1135" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1136" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1136" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>14.29%</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1137" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1137" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1138" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1138" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1139" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1139" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1140" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1140" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1141" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1141" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1142" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1142" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1143" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1143" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1144" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1144" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B1145" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1145" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1146" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>8.75%</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1147" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1147" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>319</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1148" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1148" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1149" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1150" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1151" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1152" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1153" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1154" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>2.33%</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1155" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1156" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1157" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1158" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1159" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1160" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1160" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1161" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1162" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1162" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1163" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1164" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1165" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1166" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1167" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1167"/>
+  <dimension ref="A1:I1233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45937,6 +45937,2580 @@
         </is>
       </c>
     </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1168" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>8.75%</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1169" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>323</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1170" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1171" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1172" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1173" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1174" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1175" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1176" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>2.33%</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1177" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1178" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1179" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1180" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1182" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1183" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1184" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1185" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1186" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1186" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1187" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1188" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1189" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1190" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>8.54%</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1191" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>338</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1192" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1192" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1193" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1193" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1194" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1194" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1195" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1196" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1197" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1198" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1198" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1199" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1200" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1201" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1202" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1202" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1203" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1204" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1205" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1206" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1207" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1208" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1208" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1209" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1210" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1210" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B1211" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1211" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1212" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>8.54%</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1213" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>343</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D1214" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1215" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D1215" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1216" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D1216" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1217" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D1217" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>720</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1218" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1218" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1219" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D1219" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>118</v>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1220" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1220" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1221" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D1221" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1222" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D1222" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1223" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D1223" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1224" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D1224" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1225" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D1225" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1226" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D1226" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1227" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D1227" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1228" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D1228" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1229" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D1229" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1230" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1230" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1231" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D1231" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1232" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D1232" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>121</v>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="B1233" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D1233" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>104</v>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
